--- a/data/processed/positivacao/2023-12_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2023-12_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26219,7 +26219,7 @@
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B996" t="inlineStr"/>
@@ -37545,7 +37545,7 @@
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1432" t="inlineStr"/>
@@ -66255,7 +66255,7 @@
     <row r="2537">
       <c r="A2537" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2537" t="inlineStr"/>
@@ -67900,12 +67900,12 @@
       <c r="A2601" t="inlineStr"/>
       <c r="B2601" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 4 cliente(s), não positivou 83 cliente(s) - Total vendido: R$ 6.008,71
+          <t>Vendedor 1 - VENDEDOR 01: positivou 4 cliente(s), não positivou 83 cliente(s) - Total vendido: R$ 6.008,71
 Vendedor 18 - LOJA: positivou 189 cliente(s), não positivou 710 cliente(s) - Total vendido: R$ 101.434,02
-Vendedor 3 - FERNANDA: positivou 113 cliente(s), não positivou 322 cliente(s) - Total vendido: R$ 160.264,16
-Vendedor 4 - DANIELA: positivou 100 cliente(s), não positivou 560 cliente(s) - Total vendido: R$ 57.569,32
+Vendedor 3 - VENDEDOR 03: positivou 113 cliente(s), não positivou 322 cliente(s) - Total vendido: R$ 160.264,16
+Vendedor 4 - VENDEDOR 04: positivou 100 cliente(s), não positivou 560 cliente(s) - Total vendido: R$ 57.569,32
 Vendedor 5 - SITE: positivou 9 cliente(s), não positivou 434 cliente(s) - Total vendido: R$ 1.392,10
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 62 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 62 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2601" t="inlineStr"/>
